--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.96011447453274</v>
+        <v>6.00601860211157</v>
       </c>
       <c r="D2" t="n">
-        <v>36.8418107909589</v>
+        <v>5.986794253530821</v>
       </c>
       <c r="E2" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F2" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.66782464720447</v>
+        <v>5.146021505170726</v>
       </c>
       <c r="D3" t="n">
-        <v>31.73731079539922</v>
+        <v>5.157313004252374</v>
       </c>
       <c r="E3" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F3" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.1771265599835</v>
+        <v>5.553783065997319</v>
       </c>
       <c r="D4" t="n">
-        <v>34.3369219214532</v>
+        <v>5.579749812236145</v>
       </c>
       <c r="E4" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F4" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.00334377643728</v>
+        <v>6.500543363671059</v>
       </c>
       <c r="D5" t="n">
-        <v>39.76376993374338</v>
+        <v>6.461612614233299</v>
       </c>
       <c r="E5" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F5" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.0043765239955</v>
+        <v>7.80071118514927</v>
       </c>
       <c r="D6" t="n">
-        <v>13.98588735361957</v>
+        <v>2.27270669496318</v>
       </c>
       <c r="E6" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F6" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.48179687650785</v>
+        <v>4.953291992432526</v>
       </c>
       <c r="D7" t="n">
-        <v>30.77280474370098</v>
+        <v>5.00058077085141</v>
       </c>
       <c r="E7" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F7" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.66991622531297</v>
+        <v>4.658861386613357</v>
       </c>
       <c r="D8" t="n">
-        <v>11.80042372120595</v>
+        <v>1.917568854695966</v>
       </c>
       <c r="E8" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F8" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.986203586795451</v>
+        <v>1.135258082854261</v>
       </c>
       <c r="D9" t="n">
-        <v>6.777958769397755</v>
+        <v>1.101418300027135</v>
       </c>
       <c r="E9" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F9" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.13245941035817</v>
+        <v>4.896524654183202</v>
       </c>
       <c r="D10" t="n">
-        <v>19.8395482823333</v>
+        <v>3.223926595879162</v>
       </c>
       <c r="E10" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F10" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.488668577691003</v>
+        <v>0.566908643874788</v>
       </c>
       <c r="D11" t="n">
-        <v>3.736125398039286</v>
+        <v>0.607120377181384</v>
       </c>
       <c r="E11" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F11" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.60798267286438</v>
+        <v>4.811297184340462</v>
       </c>
       <c r="D12" t="n">
-        <v>29.93077092817201</v>
+        <v>4.863750275827951</v>
       </c>
       <c r="E12" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F12" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.61602321887626</v>
+        <v>3.187603773067393</v>
       </c>
       <c r="D13" t="n">
-        <v>19.26277342155632</v>
+        <v>3.130200681002902</v>
       </c>
       <c r="E13" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F13" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.64211610861111</v>
+        <v>2.866843867649306</v>
       </c>
       <c r="D14" t="n">
-        <v>32.88974579400573</v>
+        <v>5.344583691525931</v>
       </c>
       <c r="E14" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F14" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.0561984906987</v>
+        <v>4.07163225473854</v>
       </c>
       <c r="D15" t="n">
-        <v>29.29039295910053</v>
+        <v>4.759688855853835</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F15" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.42162152194184</v>
+        <v>2.343513497315549</v>
       </c>
       <c r="D16" t="n">
-        <v>14.68766680542403</v>
+        <v>2.386745855881405</v>
       </c>
       <c r="E16" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F16" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.99675979158652</v>
+        <v>1.949473466132809</v>
       </c>
       <c r="D17" t="n">
-        <v>11.87311340893313</v>
+        <v>1.929380928951634</v>
       </c>
       <c r="E17" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F17" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>4.146989042320598</v>
+        <v>0.6738857193770972</v>
       </c>
       <c r="D18" t="n">
-        <v>4.411712898282825</v>
+        <v>0.7169033459709591</v>
       </c>
       <c r="E18" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F18" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>5.469780910965062</v>
+        <v>0.8888393980318225</v>
       </c>
       <c r="D19" t="n">
-        <v>35.77249231105245</v>
+        <v>5.813030000546022</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F19" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>13.66323350331537</v>
+        <v>2.220275444288748</v>
       </c>
       <c r="D20" t="n">
-        <v>13.55293248020616</v>
+        <v>2.2023515280335</v>
       </c>
       <c r="E20" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F20" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>17.30686357513779</v>
+        <v>2.81236533095989</v>
       </c>
       <c r="D21" t="n">
-        <v>30.94824968579631</v>
+        <v>5.029090573941899</v>
       </c>
       <c r="E21" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F21" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>28.21162483695737</v>
+        <v>4.584389036005573</v>
       </c>
       <c r="D22" t="n">
-        <v>30.20167126382378</v>
+        <v>4.907771580371365</v>
       </c>
       <c r="E22" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F22" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.741013558698516</v>
+        <v>1.582914703288509</v>
       </c>
       <c r="D23" t="n">
-        <v>39.58825490777292</v>
+        <v>6.4330914225131</v>
       </c>
       <c r="E23" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F23" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>36.33107479097266</v>
+        <v>5.903799653533058</v>
       </c>
       <c r="D24" t="n">
-        <v>36.42841075405755</v>
+        <v>5.919616747534352</v>
       </c>
       <c r="E24" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F24" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>17.45053125266593</v>
+        <v>2.835711328558213</v>
       </c>
       <c r="D25" t="n">
-        <v>17.67762284565359</v>
+        <v>2.872613712418708</v>
       </c>
       <c r="E25" t="n">
-        <v>12.17425025577515</v>
+        <v>1.978315666563461</v>
       </c>
       <c r="F25" t="n">
-        <v>11.46308934267536</v>
+        <v>1.862752018184746</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
